--- a/Heuristic/data/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/production_capacity_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27830"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5E243724-40D6-4E5E-83F5-BA2AA533A408}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC56E01-CAF7-4BCF-8905-0C0C46C532B9}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="13" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -446,6 +446,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">

--- a/Heuristic/data/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/production_capacity_scenarios.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDC56E01-CAF7-4BCF-8905-0C0C46C532B9}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CC4CA9C-AA3A-40EA-876D-4C27841E7D90}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -157,6 +157,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -448,6 +452,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">

--- a/Heuristic/data/production_capacity_scenarios.xlsx
+++ b/Heuristic/data/production_capacity_scenarios.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/5e6b18ad1acc1266/Desktop/Vaccine_Tender/Heuristic/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5CC4CA9C-AA3A-40EA-876D-4C27841E7D90}"/>
+  <xr:revisionPtr revIDLastSave="22" documentId="13_ncr:1_{6259234B-0F6C-41FA-846B-135095B5B389}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86272943-06B5-4C30-ABE7-E69BDA6E5234}"/>
   <bookViews>
-    <workbookView xWindow="13550" yWindow="-7070" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-19310" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="base_capacity" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,20 @@
     <sheet name="other_scenario" sheetId="13" r:id="rId13"/>
     <sheet name="other_scenario_scaled" sheetId="14" r:id="rId14"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -137,11 +150,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -452,7 +466,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="7" width="10.28515625" bestFit="1" customWidth="1"/>
+    <col min="8" max="11" width="10" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.25">
@@ -494,34 +509,34 @@
       <c r="A2" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="2">
         <v>7711003</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="2">
         <v>7711003</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="2">
         <v>7711003</v>
       </c>
-      <c r="E2">
+      <c r="E2" s="2">
         <v>7711003</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="2">
         <v>7711003</v>
       </c>
-      <c r="G2">
+      <c r="G2" s="2">
         <v>7711003</v>
       </c>
-      <c r="H2">
+      <c r="H2" s="2">
         <v>7711003</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="2">
         <v>7711003</v>
       </c>
-      <c r="J2">
+      <c r="J2" s="2">
         <v>7711003</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="2">
         <v>7711003</v>
       </c>
     </row>
@@ -529,34 +544,34 @@
       <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="2">
         <v>39223956</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="2">
         <v>39223956</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="2">
         <v>39223956</v>
       </c>
-      <c r="E3">
+      <c r="E3" s="2">
         <v>39223956</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="2">
         <v>39223956</v>
       </c>
-      <c r="G3">
+      <c r="G3" s="2">
         <v>39223956</v>
       </c>
-      <c r="H3">
+      <c r="H3" s="2">
         <v>39223956</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="2">
         <v>39223956</v>
       </c>
-      <c r="J3">
+      <c r="J3" s="2">
         <v>39223956</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="2">
         <v>39223956</v>
       </c>
     </row>
@@ -564,34 +579,34 @@
       <c r="A4" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="2">
         <v>61029105</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="2">
         <v>61029105</v>
       </c>
-      <c r="D4">
+      <c r="D4" s="2">
         <v>61029105</v>
       </c>
-      <c r="E4">
+      <c r="E4" s="2">
         <v>61029105</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="2">
         <v>61029105</v>
       </c>
-      <c r="G4">
+      <c r="G4" s="2">
         <v>61029105</v>
       </c>
-      <c r="H4">
+      <c r="H4" s="2">
         <v>61029105</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="2">
         <v>61029105</v>
       </c>
-      <c r="J4">
+      <c r="J4" s="2">
         <v>61029105</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="2">
         <v>61029105</v>
       </c>
     </row>
@@ -599,34 +614,34 @@
       <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="2">
         <v>12048153</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>12048153</v>
       </c>
-      <c r="D5">
+      <c r="D5" s="2">
         <v>12048153</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>12048153</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>12048153</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>12048153</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>12048153</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>12048153</v>
       </c>
-      <c r="J5">
+      <c r="J5" s="2">
         <v>12048153</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="2">
         <v>12048153</v>
       </c>
     </row>
@@ -634,34 +649,34 @@
       <c r="A6" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="2">
         <v>164885690</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="2">
         <v>164885690</v>
       </c>
-      <c r="D6">
+      <c r="D6" s="2">
         <v>164885690</v>
       </c>
-      <c r="E6">
+      <c r="E6" s="2">
         <v>164885690</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="2">
         <v>164885690</v>
       </c>
-      <c r="G6">
+      <c r="G6" s="2">
         <v>164885690</v>
       </c>
-      <c r="H6">
+      <c r="H6" s="2">
         <v>164885690</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="2">
         <v>164885690</v>
       </c>
-      <c r="J6">
+      <c r="J6" s="2">
         <v>164885690</v>
       </c>
-      <c r="K6">
+      <c r="K6" s="2">
         <v>164885690</v>
       </c>
     </row>
@@ -669,34 +684,34 @@
       <c r="A7" t="s">
         <v>6</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="2">
         <v>12812242</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="2">
         <v>12812242</v>
       </c>
-      <c r="D7">
+      <c r="D7" s="2">
         <v>12812242</v>
       </c>
-      <c r="E7">
+      <c r="E7" s="2">
         <v>12812242</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="2">
         <v>12812242</v>
       </c>
-      <c r="G7">
+      <c r="G7" s="2">
         <v>12812242</v>
       </c>
-      <c r="H7">
+      <c r="H7" s="2">
         <v>12812242</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="2">
         <v>12812242</v>
       </c>
-      <c r="J7">
+      <c r="J7" s="2">
         <v>12812242</v>
       </c>
-      <c r="K7">
+      <c r="K7" s="2">
         <v>12812242</v>
       </c>
     </row>
@@ -704,34 +719,34 @@
       <c r="A8" t="s">
         <v>7</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="2">
         <v>226762686</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="2">
         <v>226762686</v>
       </c>
-      <c r="D8">
+      <c r="D8" s="2">
         <v>226762686</v>
       </c>
-      <c r="E8">
+      <c r="E8" s="2">
         <v>226762686</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="2">
         <v>226762686</v>
       </c>
-      <c r="G8">
+      <c r="G8" s="2">
         <v>226762686</v>
       </c>
-      <c r="H8">
+      <c r="H8" s="2">
         <v>226762686</v>
       </c>
-      <c r="I8">
+      <c r="I8" s="2">
         <v>226762686</v>
       </c>
-      <c r="J8">
+      <c r="J8" s="2">
         <v>226762686</v>
       </c>
-      <c r="K8">
+      <c r="K8" s="2">
         <v>226762686</v>
       </c>
     </row>
@@ -739,34 +754,34 @@
       <c r="A9" t="s">
         <v>8</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="2">
         <v>80972855</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="2">
         <v>80972855</v>
       </c>
-      <c r="D9">
+      <c r="D9" s="2">
         <v>80972855</v>
       </c>
-      <c r="E9">
+      <c r="E9" s="2">
         <v>80972855</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="2">
         <v>80972855</v>
       </c>
-      <c r="G9">
+      <c r="G9" s="2">
         <v>80972855</v>
       </c>
-      <c r="H9">
+      <c r="H9" s="2">
         <v>80972855</v>
       </c>
-      <c r="I9">
+      <c r="I9" s="2">
         <v>80972855</v>
       </c>
-      <c r="J9">
+      <c r="J9" s="2">
         <v>80972855</v>
       </c>
-      <c r="K9">
+      <c r="K9" s="2">
         <v>80972855</v>
       </c>
     </row>
@@ -774,34 +789,34 @@
       <c r="A10" t="s">
         <v>9</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="2">
         <v>43702188</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="2">
         <v>43702188</v>
       </c>
-      <c r="D10">
+      <c r="D10" s="2">
         <v>43702188</v>
       </c>
-      <c r="E10">
+      <c r="E10" s="2">
         <v>43702188</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="2">
         <v>43702188</v>
       </c>
-      <c r="G10">
+      <c r="G10" s="2">
         <v>43702188</v>
       </c>
-      <c r="H10">
+      <c r="H10" s="2">
         <v>43702188</v>
       </c>
-      <c r="I10">
+      <c r="I10" s="2">
         <v>43702188</v>
       </c>
-      <c r="J10">
+      <c r="J10" s="2">
         <v>43702188</v>
       </c>
-      <c r="K10">
+      <c r="K10" s="2">
         <v>43702188</v>
       </c>
     </row>
@@ -809,34 +824,34 @@
       <c r="A11" t="s">
         <v>10</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="2">
         <v>56991052</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="2">
         <v>56991052</v>
       </c>
-      <c r="D11">
+      <c r="D11" s="2">
         <v>56991052</v>
       </c>
-      <c r="E11">
+      <c r="E11" s="2">
         <v>56991052</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="2">
         <v>56991052</v>
       </c>
-      <c r="G11">
+      <c r="G11" s="2">
         <v>56991052</v>
       </c>
-      <c r="H11">
+      <c r="H11" s="2">
         <v>56991052</v>
       </c>
-      <c r="I11">
+      <c r="I11" s="2">
         <v>56991052</v>
       </c>
-      <c r="J11">
+      <c r="J11" s="2">
         <v>56991052</v>
       </c>
-      <c r="K11">
+      <c r="K11" s="2">
         <v>56991052</v>
       </c>
     </row>
@@ -844,34 +859,34 @@
       <c r="A12" t="s">
         <v>11</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="2">
         <v>45911731</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>45911731</v>
       </c>
-      <c r="D12">
+      <c r="D12" s="2">
         <v>45911731</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>45911731</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>45911731</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>45911731</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>45911731</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>45911731</v>
       </c>
-      <c r="J12">
+      <c r="J12" s="2">
         <v>45911731</v>
       </c>
-      <c r="K12">
+      <c r="K12" s="2">
         <v>45911731</v>
       </c>
     </row>
@@ -879,34 +894,34 @@
       <c r="A13" t="s">
         <v>12</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="2">
         <v>10874165</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="2">
         <v>10874165</v>
       </c>
-      <c r="D13">
+      <c r="D13" s="2">
         <v>10874165</v>
       </c>
-      <c r="E13">
+      <c r="E13" s="2">
         <v>10874165</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="2">
         <v>10874165</v>
       </c>
-      <c r="G13">
+      <c r="G13" s="2">
         <v>10874165</v>
       </c>
-      <c r="H13">
+      <c r="H13" s="2">
         <v>10874165</v>
       </c>
-      <c r="I13">
+      <c r="I13" s="2">
         <v>10874165</v>
       </c>
-      <c r="J13">
+      <c r="J13" s="2">
         <v>10874165</v>
       </c>
-      <c r="K13">
+      <c r="K13" s="2">
         <v>10874165</v>
       </c>
     </row>
@@ -914,34 +929,34 @@
       <c r="A14" t="s">
         <v>13</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="2">
         <v>83916974</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="2">
         <v>83916974</v>
       </c>
-      <c r="D14">
+      <c r="D14" s="2">
         <v>83916974</v>
       </c>
-      <c r="E14">
+      <c r="E14" s="2">
         <v>83916974</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="2">
         <v>83916974</v>
       </c>
-      <c r="G14">
+      <c r="G14" s="2">
         <v>83916974</v>
       </c>
-      <c r="H14">
+      <c r="H14" s="2">
         <v>83916974</v>
       </c>
-      <c r="I14">
+      <c r="I14" s="2">
         <v>83916974</v>
       </c>
-      <c r="J14">
+      <c r="J14" s="2">
         <v>83916974</v>
       </c>
-      <c r="K14">
+      <c r="K14" s="2">
         <v>83916974</v>
       </c>
     </row>
@@ -949,34 +964,34 @@
       <c r="A15" t="s">
         <v>14</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="2">
         <v>87429432</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="2">
         <v>87429432</v>
       </c>
-      <c r="D15">
+      <c r="D15" s="2">
         <v>87429432</v>
       </c>
-      <c r="E15">
+      <c r="E15" s="2">
         <v>87429432</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="2">
         <v>87429432</v>
       </c>
-      <c r="G15">
+      <c r="G15" s="2">
         <v>87429432</v>
       </c>
-      <c r="H15">
+      <c r="H15" s="2">
         <v>87429432</v>
       </c>
-      <c r="I15">
+      <c r="I15" s="2">
         <v>87429432</v>
       </c>
-      <c r="J15">
+      <c r="J15" s="2">
         <v>87429432</v>
       </c>
-      <c r="K15">
+      <c r="K15" s="2">
         <v>87429432</v>
       </c>
     </row>
@@ -984,34 +999,34 @@
       <c r="A16" t="s">
         <v>15</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="2">
         <v>587114096</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="2">
         <v>587114096</v>
       </c>
-      <c r="D16">
+      <c r="D16" s="2">
         <v>587114096</v>
       </c>
-      <c r="E16">
+      <c r="E16" s="2">
         <v>587114096</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="2">
         <v>587114096</v>
       </c>
-      <c r="G16">
+      <c r="G16" s="2">
         <v>587114096</v>
       </c>
-      <c r="H16">
+      <c r="H16" s="2">
         <v>587114096</v>
       </c>
-      <c r="I16">
+      <c r="I16" s="2">
         <v>587114096</v>
       </c>
-      <c r="J16">
+      <c r="J16" s="2">
         <v>587114096</v>
       </c>
-      <c r="K16">
+      <c r="K16" s="2">
         <v>587114096</v>
       </c>
     </row>
